--- a/data/trans_orig/RUIDO_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>25906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>28311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44880</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>23388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20251</t>
+          <t>20597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26219</t>
+          <t>26249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23805</t>
+          <t>23967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>35691</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36769</t>
+          <t>36801</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55363</t>
+          <t>55584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64510</t>
+          <t>65091</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87647</t>
+          <t>86556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30565</t>
+          <t>29273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40813</t>
+          <t>39879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25437</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18094</t>
+          <t>18615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63312</t>
+          <t>63642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>31616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43953</t>
+          <t>43122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102546</t>
+          <t>102416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34311</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20577</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63217</t>
+          <t>64470</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12686</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>24781</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>43942</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>34226</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45435</t>
+          <t>45118</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65274</t>
+          <t>64885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>14907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18297</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>30907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139688</t>
+          <t>133228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>83941</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>122321</t>
+          <t>122257</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>212552</t>
+          <t>213062</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>61501</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108560</t>
+          <t>109571</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109333</t>
+          <t>107996</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>140198</t>
+          <t>138537</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>180617</t>
+          <t>178196</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>239089</t>
+          <t>237279</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41481</t>
+          <t>42671</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>56497</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>92100</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>45477</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>48869</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77968</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13669</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8726</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5486</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13290</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21,19%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18328</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25906</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21856</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16324</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28219</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>45,47%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>33,96%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>58,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15040</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10322</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19973</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>48,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28311</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>37048</t>
+          <t>36963</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29148</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45426</t>
+          <t>44549</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7026</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12682</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4351</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8574</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7373</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12245</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>25,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8441</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4843</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13069</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23388</t>
+          <t>22439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>48069</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>48069</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>48069</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>41175</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>41175</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>41175</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>91501</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91501</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>91501</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7129</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3521</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13726</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1626</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9483</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13935</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15971</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10688</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23020</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14273</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9714</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20870</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21,88%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>31969</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23967</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42812</t>
+          <t>39441</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41352</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33353</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51175</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>34,66%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>53,18%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>29815</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23747</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>35691</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>36,41%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>54,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45526</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36801</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55584</t>
+          <t>35528</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>75340</t>
+          <t>70378</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65091</t>
+          <t>60008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>86556</t>
+          <t>81792</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22227</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15500</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30229</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8954</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5281</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14243</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30708</t>
+          <t>31281</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39879</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9552</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15571</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7362</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12073</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96231</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96231</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96231</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>65219</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>65219</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>65219</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103088</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103088</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103088</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>168306</t>
+          <t>160916</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>168306</t>
+          <t>160916</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>168306</t>
+          <t>160916</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4981</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10871</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20313</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14047</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27517</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>41475</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18615</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>63642</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>53,04%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24286</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17605</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>65760</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43122</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102416</t>
+          <t>43684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24514</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17934</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31533</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>44,94%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>32,88%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>57,81%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>20070</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7815</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34184</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>43,71%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>24590</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>47837</t>
+          <t>42552</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64470</t>
+          <t>51812</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5447</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2263</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12156</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5954</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11555</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5721</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12346</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>54545</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>54545</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>54545</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>78202</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>78202</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>78202</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>49240</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>49240</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62581</t>
+          <t>49240</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140782</t>
+          <t>103785</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140782</t>
+          <t>103785</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140782</t>
+          <t>103785</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5498</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>11499</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>4122</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1442</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8545</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>22928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>19892</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>33524</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43942</t>
+          <t>39081</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26552</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19475</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>33271</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>39,95%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>29,3%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>50,06%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>27210</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>20730</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>34226</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>38,13%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>29,05%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>47,97%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28117</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>55327</t>
+          <t>53736</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45118</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64885</t>
+          <t>63232</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8733</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4347</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14234</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>12229</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>7171</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>18553</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>17,14%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>26,0%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>28451</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9454</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>16756</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>25,21%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>12182</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>7446</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>18878</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>20841</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>66457</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>66457</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>66457</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>71355</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>71355</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>71355</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70883</t>
+          <t>68492</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70883</t>
+          <t>68492</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70883</t>
+          <t>68492</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>142237</t>
+          <t>134949</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>142237</t>
+          <t>134949</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>142237</t>
+          <t>134949</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>13761</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>18535</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>11043</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>27525</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>40020</t>
+          <t>38688</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52840</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>60904</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>49828</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>74161</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>80084</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>55157</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>133228</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>31,29%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>52,05%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>69497</t>
+          <t>49985</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83941</t>
+          <t>60425</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>149581</t>
+          <t>110889</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>122257</t>
+          <t>96899</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213062</t>
+          <t>128802</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>114274</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>101455</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>129627</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>38,24%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>48,86%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>92135</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>61501</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>109571</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>42,81%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>123418</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107996</t>
+          <t>76759</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138537</t>
+          <t>100597</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>215553</t>
+          <t>203628</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>178196</t>
+          <t>183742</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>237279</t>
+          <t>220710</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>43433</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>33970</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>56378</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>21,25%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>31489</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>21105</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>42671</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56497</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>75281</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59626</t>
+          <t>61414</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>92100</t>
+          <t>89110</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>27227</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>18777</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>37628</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>33707</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>22836</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>45477</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>17,77%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>62982</t>
+          <t>60742</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>76545</t>
+          <t>74122</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>350</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
